--- a/artfynd/A 55928-2019 artfynd.xlsx
+++ b/artfynd/A 55928-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122853111</v>
       </c>
       <c r="B2" t="n">
-        <v>94836</v>
+        <v>94844</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>122852965</v>
       </c>
       <c r="B3" t="n">
-        <v>78144</v>
+        <v>78148</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 55928-2019 artfynd.xlsx
+++ b/artfynd/A 55928-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122853111</v>
+        <v>122852965</v>
       </c>
       <c r="B2" t="n">
-        <v>94844</v>
+        <v>78148</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2671</v>
+        <v>6436</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Gulpudrad spiklav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Calicium adspersum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Pers.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tall-och ekhällar SVV om Fagerhult, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546881</v>
+        <v>546797</v>
       </c>
       <c r="R2" t="n">
-        <v>6457400</v>
+        <v>6457473</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,6 +776,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Quercus robur</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -787,10 +812,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122852965</v>
+        <v>122853111</v>
       </c>
       <c r="B3" t="n">
-        <v>78148</v>
+        <v>94844</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,42 +828,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6436</v>
+        <v>2671</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gulpudrad spiklav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Calicium adspersum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pers.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Tall-och ekhällar SVV om Fagerhult, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546797</v>
+        <v>546881</v>
       </c>
       <c r="R3" t="n">
-        <v>6457473</v>
+        <v>6457400</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +887,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +897,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,26 +908,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>skogsek</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Quercus robur</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">

--- a/artfynd/A 55928-2019 artfynd.xlsx
+++ b/artfynd/A 55928-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122852965</v>
+        <v>122853111</v>
       </c>
       <c r="B2" t="n">
-        <v>78148</v>
+        <v>94846</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,42 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6436</v>
+        <v>2671</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulpudrad spiklav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Calicium adspersum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Pers.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tall-och ekhällar SVV om Fagerhult, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546797</v>
+        <v>546881</v>
       </c>
       <c r="R2" t="n">
-        <v>6457473</v>
+        <v>6457400</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,26 +771,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>skogsek</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Quercus robur</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -812,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122853111</v>
+        <v>122852965</v>
       </c>
       <c r="B3" t="n">
-        <v>94844</v>
+        <v>78148</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -828,37 +803,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2671</v>
+        <v>6436</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Gulpudrad spiklav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Calicium adspersum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Pers.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Tall-och ekhällar SVV om Fagerhult, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546881</v>
+        <v>546797</v>
       </c>
       <c r="R3" t="n">
-        <v>6457400</v>
+        <v>6457473</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -887,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -897,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,6 +888,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Quercus robur</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">

--- a/artfynd/A 55928-2019 artfynd.xlsx
+++ b/artfynd/A 55928-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122853111</v>
+        <v>122852965</v>
       </c>
       <c r="B2" t="n">
-        <v>94846</v>
+        <v>78148</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2671</v>
+        <v>6436</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Gulpudrad spiklav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Calicium adspersum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Pers.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tall-och ekhällar SVV om Fagerhult, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546881</v>
+        <v>546797</v>
       </c>
       <c r="R2" t="n">
-        <v>6457400</v>
+        <v>6457473</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,6 +776,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Quercus robur</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -787,10 +812,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122852965</v>
+        <v>122853111</v>
       </c>
       <c r="B3" t="n">
-        <v>78148</v>
+        <v>94854</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,42 +828,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6436</v>
+        <v>2671</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gulpudrad spiklav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Calicium adspersum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pers.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Tall-och ekhällar SVV om Fagerhult, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546797</v>
+        <v>546881</v>
       </c>
       <c r="R3" t="n">
-        <v>6457473</v>
+        <v>6457400</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +887,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +897,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,26 +908,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>skogsek</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Quercus robur</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">

--- a/artfynd/A 55928-2019 artfynd.xlsx
+++ b/artfynd/A 55928-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122852965</v>
+        <v>122853111</v>
       </c>
       <c r="B2" t="n">
-        <v>78148</v>
+        <v>94854</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,42 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6436</v>
+        <v>2671</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulpudrad spiklav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Calicium adspersum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Pers.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tall-och ekhällar SVV om Fagerhult, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546797</v>
+        <v>546881</v>
       </c>
       <c r="R2" t="n">
-        <v>6457473</v>
+        <v>6457400</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,26 +771,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>skogsek</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Quercus robur</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -812,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122853111</v>
+        <v>122852965</v>
       </c>
       <c r="B3" t="n">
-        <v>94854</v>
+        <v>78148</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -828,37 +803,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2671</v>
+        <v>6436</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Gulpudrad spiklav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Calicium adspersum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Pers.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Tall-och ekhällar SVV om Fagerhult, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546881</v>
+        <v>546797</v>
       </c>
       <c r="R3" t="n">
-        <v>6457400</v>
+        <v>6457473</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -887,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -897,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,6 +888,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Quercus robur</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">

--- a/artfynd/A 55928-2019 artfynd.xlsx
+++ b/artfynd/A 55928-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122853111</v>
+        <v>122852965</v>
       </c>
       <c r="B2" t="n">
-        <v>94854</v>
+        <v>78148</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2671</v>
+        <v>6436</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Gulpudrad spiklav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Calicium adspersum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Pers.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tall-och ekhällar SVV om Fagerhult, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546881</v>
+        <v>546797</v>
       </c>
       <c r="R2" t="n">
-        <v>6457400</v>
+        <v>6457473</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,6 +776,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Quercus robur</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -787,10 +812,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122852965</v>
+        <v>122853111</v>
       </c>
       <c r="B3" t="n">
-        <v>78148</v>
+        <v>94854</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,42 +828,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6436</v>
+        <v>2671</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gulpudrad spiklav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Calicium adspersum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pers.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Tall-och ekhällar SVV om Fagerhult, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546797</v>
+        <v>546881</v>
       </c>
       <c r="R3" t="n">
-        <v>6457473</v>
+        <v>6457400</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +887,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +897,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,26 +908,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>skogsek</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Quercus robur</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">

--- a/artfynd/A 55928-2019 artfynd.xlsx
+++ b/artfynd/A 55928-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122852965</v>
+        <v>122853111</v>
       </c>
       <c r="B2" t="n">
-        <v>78148</v>
+        <v>94857</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,42 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6436</v>
+        <v>2671</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulpudrad spiklav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Calicium adspersum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Pers.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tall-och ekhällar SVV om Fagerhult, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546797</v>
+        <v>546881</v>
       </c>
       <c r="R2" t="n">
-        <v>6457473</v>
+        <v>6457400</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,26 +771,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>skogsek</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Quercus robur</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -812,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122853111</v>
+        <v>122852965</v>
       </c>
       <c r="B3" t="n">
-        <v>94854</v>
+        <v>78151</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -828,37 +803,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2671</v>
+        <v>6436</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Gulpudrad spiklav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Calicium adspersum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Pers.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Tall-och ekhällar SVV om Fagerhult, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546881</v>
+        <v>546797</v>
       </c>
       <c r="R3" t="n">
-        <v>6457400</v>
+        <v>6457473</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -887,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -897,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,6 +888,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Quercus robur</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">

--- a/artfynd/A 55928-2019 artfynd.xlsx
+++ b/artfynd/A 55928-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122853111</v>
       </c>
       <c r="B2" t="n">
-        <v>94857</v>
+        <v>94859</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>122852965</v>
       </c>
       <c r="B3" t="n">
-        <v>78151</v>
+        <v>78153</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 55928-2019 artfynd.xlsx
+++ b/artfynd/A 55928-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122853111</v>
+        <v>122852965</v>
       </c>
       <c r="B2" t="n">
-        <v>94859</v>
+        <v>78154</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2671</v>
+        <v>6436</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Gulpudrad spiklav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Calicium adspersum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Pers.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tall-och ekhällar SVV om Fagerhult, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546881</v>
+        <v>546797</v>
       </c>
       <c r="R2" t="n">
-        <v>6457400</v>
+        <v>6457473</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,6 +776,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Quercus robur</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -787,10 +812,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122852965</v>
+        <v>122853111</v>
       </c>
       <c r="B3" t="n">
-        <v>78153</v>
+        <v>94865</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,42 +828,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6436</v>
+        <v>2671</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gulpudrad spiklav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Calicium adspersum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pers.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Tall-och ekhällar SVV om Fagerhult, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546797</v>
+        <v>546881</v>
       </c>
       <c r="R3" t="n">
-        <v>6457473</v>
+        <v>6457400</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +887,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +897,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,26 +908,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>skogsek</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Quercus robur</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">

--- a/artfynd/A 55928-2019 artfynd.xlsx
+++ b/artfynd/A 55928-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122852965</v>
+        <v>122853111</v>
       </c>
       <c r="B2" t="n">
-        <v>78154</v>
+        <v>94868</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,42 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6436</v>
+        <v>2671</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulpudrad spiklav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Calicium adspersum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Pers.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tall-och ekhällar SVV om Fagerhult, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546797</v>
+        <v>546881</v>
       </c>
       <c r="R2" t="n">
-        <v>6457473</v>
+        <v>6457400</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,26 +771,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>skogsek</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Quercus robur</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -812,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122853111</v>
+        <v>122852965</v>
       </c>
       <c r="B3" t="n">
-        <v>94865</v>
+        <v>78157</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -828,37 +803,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2671</v>
+        <v>6436</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Gulpudrad spiklav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Calicium adspersum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Pers.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Tall-och ekhällar SVV om Fagerhult, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546881</v>
+        <v>546797</v>
       </c>
       <c r="R3" t="n">
-        <v>6457400</v>
+        <v>6457473</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -887,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -897,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,6 +888,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Quercus robur</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
